--- a/fl-structure-2.2.0/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
+++ b/fl-structure-2.2.0/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-07T13:17:22+00:00</t>
+    <t>2026-02-07T19:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
